--- a/excel-files/TAGUIG_PATEROS/CAPT. HIPOLITO FRANCISCO ELEMENTARY SCHOOL - MAIN.xlsx
+++ b/excel-files/TAGUIG_PATEROS/CAPT. HIPOLITO FRANCISCO ELEMENTARY SCHOOL - MAIN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4844945-3C72-476C-AF5C-AFAC7920A934}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{191FBEE6-C24A-49C3-86A9-88E3354EA3E5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="91">
   <si>
     <t>Grade Level</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Statistics and Probability</t>
+  </si>
+  <si>
+    <t>i</t>
   </si>
   <si>
     <t>QUARTER 1</t>
@@ -747,6 +750,13 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -758,13 +768,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3476,7 +3479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -4416,11 +4419,11 @@
     <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="44">
+      <c r="C50" s="40">
         <f>C2+C8+C14+C21+C31+C41</f>
         <v>0</v>
       </c>
-      <c r="D50" s="44">
+      <c r="D50" s="40">
         <f>SUBTOTAL(109,D2:D49)</f>
         <v>0</v>
       </c>
@@ -5309,7 +5312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:10" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -5329,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:10" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>23</v>
       </c>
@@ -5347,6 +5350,11 @@
       <c r="H98" s="4">
         <f t="shared" si="19"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="J111" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -5403,38 +5411,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="D1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5447,81 +5455,81 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="M2" s="41" t="s">
         <v>46</v>
       </c>
+      <c r="N2" s="41" t="s">
+        <v>47</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y2" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="Y2" s="42" t="s">
         <v>58</v>
       </c>
+      <c r="Z2" s="42" t="s">
+        <v>59</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="30.6" customHeight="1">
       <c r="A3" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -6086,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="5">
@@ -6651,7 +6659,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="5">
@@ -7286,7 +7294,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -13607,38 +13615,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="D1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13651,76 +13659,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="45" t="s">
+      <c r="M2" s="41" t="s">
         <v>72</v>
       </c>
+      <c r="N2" s="41" t="s">
+        <v>73</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y2" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="Y2" s="42" t="s">
         <v>84</v>
       </c>
+      <c r="Z2" s="42" t="s">
+        <v>85</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="19.149999999999999">
@@ -14211,7 +14219,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -14764,7 +14772,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -15386,7 +15394,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -15870,7 +15878,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15939,7 +15947,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16077,7 +16085,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16146,7 +16154,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16630,7 +16638,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16699,7 +16707,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16837,7 +16845,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16906,7 +16914,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17390,7 +17398,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17459,7 +17467,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17597,7 +17605,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17666,7 +17674,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -18150,7 +18158,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18219,7 +18227,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18357,7 +18365,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18426,7 +18434,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18910,7 +18918,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -18979,7 +18987,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19117,7 +19125,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19186,7 +19194,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19670,7 +19678,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -19739,7 +19747,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -19877,7 +19885,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -19946,7 +19954,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20430,7 +20438,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20499,7 +20507,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20637,7 +20645,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -20706,7 +20714,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
